--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125715151</v>
+        <v>125715654</v>
       </c>
       <c r="B2" t="n">
-        <v>97202</v>
+        <v>79556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388542</v>
+        <v>388701</v>
       </c>
       <c r="R2" t="n">
-        <v>6849505</v>
+        <v>6849667</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,11 +769,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,51 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125715654</v>
+        <v>125715151</v>
       </c>
       <c r="B3" t="n">
-        <v>79556</v>
+        <v>97209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388701</v>
+        <v>388542</v>
       </c>
       <c r="R3" t="n">
-        <v>6849667</v>
+        <v>6849505</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +876,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>125715063</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>98248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125715654</v>
+        <v>125715151</v>
       </c>
       <c r="B2" t="n">
-        <v>79556</v>
+        <v>97209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388701</v>
+        <v>388542</v>
       </c>
       <c r="R2" t="n">
-        <v>6849667</v>
+        <v>6849505</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,48 +787,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125715151</v>
+        <v>125715654</v>
       </c>
       <c r="B3" t="n">
-        <v>97209</v>
+        <v>79556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388542</v>
+        <v>388701</v>
       </c>
       <c r="R3" t="n">
-        <v>6849505</v>
+        <v>6849667</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,11 +881,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125715151</v>
       </c>
       <c r="B2" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125715654</v>
       </c>
       <c r="B3" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>125716673</v>
       </c>
       <c r="B4" t="n">
-        <v>79062</v>
+        <v>79063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125716278</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>125715063</v>
       </c>
       <c r="B7" t="n">
-        <v>98248</v>
+        <v>98251</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>125716912</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>125715362</v>
       </c>
       <c r="B10" t="n">
-        <v>77916</v>
+        <v>77917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125715151</v>
       </c>
       <c r="B2" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125715654</v>
       </c>
       <c r="B3" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>125716673</v>
       </c>
       <c r="B4" t="n">
-        <v>79063</v>
+        <v>79067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,48 +1127,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125716278</v>
+        <v>125715063</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>98255</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388845</v>
+        <v>388542</v>
       </c>
       <c r="R6" t="n">
-        <v>6849690</v>
+        <v>6849505</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,49 +1238,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125715063</v>
+        <v>125716278</v>
       </c>
       <c r="B7" t="n">
-        <v>98251</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388542</v>
+        <v>388845</v>
       </c>
       <c r="R7" t="n">
-        <v>6849505</v>
+        <v>6849690</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
         <v>125716912</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>125715362</v>
       </c>
       <c r="B10" t="n">
-        <v>77917</v>
+        <v>77921</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125715151</v>
       </c>
       <c r="B2" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125715063</v>
       </c>
       <c r="B6" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -1127,49 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125715063</v>
+        <v>125716278</v>
       </c>
       <c r="B6" t="n">
-        <v>98256</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388542</v>
+        <v>388845</v>
       </c>
       <c r="R6" t="n">
-        <v>6849505</v>
+        <v>6849690</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,48 +1237,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125716278</v>
+        <v>125715063</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>98256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388845</v>
+        <v>388542</v>
       </c>
       <c r="R7" t="n">
-        <v>6849690</v>
+        <v>6849505</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125715151</v>
+        <v>125715654</v>
       </c>
       <c r="B2" t="n">
-        <v>97217</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388542</v>
+        <v>388701</v>
       </c>
       <c r="R2" t="n">
-        <v>6849505</v>
+        <v>6849667</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,11 +769,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,51 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125715654</v>
+        <v>125715151</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>97219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388701</v>
+        <v>388542</v>
       </c>
       <c r="R3" t="n">
-        <v>6849667</v>
+        <v>6849505</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +876,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>125716673</v>
       </c>
       <c r="B4" t="n">
-        <v>79067</v>
+        <v>79068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>125716278</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>125715063</v>
       </c>
       <c r="B7" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>125716912</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>125715362</v>
       </c>
       <c r="B10" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>125715151</v>
       </c>
       <c r="B3" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>125715063</v>
       </c>
       <c r="B7" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125715654</v>
+        <v>125715151</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>97221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388701</v>
+        <v>388542</v>
       </c>
       <c r="R2" t="n">
-        <v>6849667</v>
+        <v>6849505</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,48 +787,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125715151</v>
+        <v>125715654</v>
       </c>
       <c r="B3" t="n">
-        <v>97221</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388542</v>
+        <v>388701</v>
       </c>
       <c r="R3" t="n">
-        <v>6849505</v>
+        <v>6849667</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,11 +881,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125715151</v>
+        <v>125715654</v>
       </c>
       <c r="B2" t="n">
-        <v>97221</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388542</v>
+        <v>388701</v>
       </c>
       <c r="R2" t="n">
-        <v>6849505</v>
+        <v>6849667</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,11 +769,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,51 +785,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125715654</v>
+        <v>125715151</v>
       </c>
       <c r="B3" t="n">
-        <v>79562</v>
+        <v>97223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388701</v>
+        <v>388542</v>
       </c>
       <c r="R3" t="n">
-        <v>6849667</v>
+        <v>6849505</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +876,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,48 +1127,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125716278</v>
+        <v>125715063</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>98262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388845</v>
+        <v>388542</v>
       </c>
       <c r="R6" t="n">
-        <v>6849690</v>
+        <v>6849505</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,49 +1238,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125715063</v>
+        <v>125716278</v>
       </c>
       <c r="B7" t="n">
-        <v>98260</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388542</v>
+        <v>388845</v>
       </c>
       <c r="R7" t="n">
-        <v>6849505</v>
+        <v>6849690</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125715654</v>
+        <v>125715151</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>97227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388701</v>
+        <v>388542</v>
       </c>
       <c r="R2" t="n">
-        <v>6849667</v>
+        <v>6849505</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,48 +787,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125715151</v>
+        <v>125715654</v>
       </c>
       <c r="B3" t="n">
-        <v>97223</v>
+        <v>79566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388542</v>
+        <v>388701</v>
       </c>
       <c r="R3" t="n">
-        <v>6849505</v>
+        <v>6849667</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,11 +881,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>125716673</v>
       </c>
       <c r="B4" t="n">
-        <v>79068</v>
+        <v>79072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,49 +1127,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125715063</v>
+        <v>125716278</v>
       </c>
       <c r="B6" t="n">
-        <v>98262</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vallmyran, Dlr</t>
+          <t>Flarkmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388542</v>
+        <v>388845</v>
       </c>
       <c r="R6" t="n">
-        <v>6849505</v>
+        <v>6849690</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1201,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,48 +1237,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125716278</v>
+        <v>125715063</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>98266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flarkmyran, Dlr</t>
+          <t>Vallmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388845</v>
+        <v>388542</v>
       </c>
       <c r="R7" t="n">
-        <v>6849690</v>
+        <v>6849505</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
         <v>125716912</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>125715362</v>
       </c>
       <c r="B10" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125715151</v>
       </c>
       <c r="B2" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>125714735</v>
       </c>
       <c r="B5" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>125715063</v>
       </c>
       <c r="B7" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1814,6 +1814,354 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128715468</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vallmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>388487</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6849540</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128715466</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vallmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>388469</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6849492</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128715467</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vallmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>388443</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6849494</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>128715468</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128715466</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128715467</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>128715468</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>128715468</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128715466</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128715467</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>128715468</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128715466</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128715467</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>128715468</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>128715468</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128715466</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128715467</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -1819,7 +1819,7 @@
         <v>128715468</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128715466</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128715467</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23427-2025 artfynd.xlsx
+++ b/artfynd/A 23427-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125716673</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125716278</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125716912</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128715468</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715565</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715362</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715841</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128715466</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128715467</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715910</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2046,6 +2106,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125716866</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2170,6 +2235,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125717003</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2281,6 +2351,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715063</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2392,6 +2467,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125714735</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2504,6 +2584,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715151</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2614,6 +2699,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715654</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,8 +2814,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125715801</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>